--- a/04-BOM/Gyro_Subsystem_BOM.xlsx
+++ b/04-BOM/Gyro_Subsystem_BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arizonastateu-my.sharepoint.com/personal/rrangasa_sundevils_asu_edu/Documents/College/SEM 6/EGR 314/Gyro_Subsystem/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rgrag\Documents\EGR314raj.github.io\docs\04-BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_07F510ADD3405E515D34DBB0535ED87656CD902A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D746F35C-82F5-4BCF-8D93-4E3C473952AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="151">
   <si>
     <t>Gyro Subsystem - Bill of Materials</t>
   </si>
@@ -134,24 +134,6 @@
     <t>U4</t>
   </si>
   <si>
-    <t>MPU-9250 9-Axis IMU Breakout Board (Gyro/Accel/Mag)</t>
-  </si>
-  <si>
-    <t>SparkFun / InvenSense</t>
-  </si>
-  <si>
-    <t>SEN-13762</t>
-  </si>
-  <si>
-    <t>https://www.sparkfun.com/products/13762</t>
-  </si>
-  <si>
-    <t>https://invensense.tdk.com/wp-content/uploads/2015/02/PS-MPU-9250A-01-v1.1.pdf</t>
-  </si>
-  <si>
-    <t>SparkFun</t>
-  </si>
-  <si>
     <t>MCP9250-BREAKOUT-BOARD1</t>
   </si>
   <si>
@@ -492,6 +474,18 @@
   </si>
   <si>
     <t>TP1-TP33 (as populated)</t>
+  </si>
+  <si>
+    <t>LSM9DS1 9-Axis IMU Breakout Board (Gyro/Accel/Mag)</t>
+  </si>
+  <si>
+    <t>Audafruit</t>
+  </si>
+  <si>
+    <t>1528-1900-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/3387/6623863</t>
   </si>
 </sst>
 </file>
@@ -501,7 +495,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,6 +512,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -558,10 +560,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -570,8 +573,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1069,42 +1074,42 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="E5" s="3">
-        <v>12</v>
+        <v>22.5</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>22.5</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>37</v>
+        <v>149</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -1114,12 +1119,12 @@
         <v>-1</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -1139,22 +1144,22 @@
         <v>0.3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -1164,12 +1169,12 @@
         <v>-1</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -1189,20 +1194,20 @@
         <v>0.3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -1212,12 +1217,12 @@
         <v>-2</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
@@ -1237,20 +1242,20 @@
         <v>0.2</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -1260,12 +1265,12 @@
         <v>-1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -1285,20 +1290,20 @@
         <v>0.2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -1308,12 +1313,12 @@
         <v>-1</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
@@ -1333,20 +1338,20 @@
         <v>0.24</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1356,12 +1361,12 @@
         <v>-3</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -1381,20 +1386,20 @@
         <v>0.3</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -1404,12 +1409,12 @@
         <v>-1</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1429,20 +1434,20 @@
         <v>0.8</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -1452,12 +1457,12 @@
         <v>-2</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B13" s="2">
         <v>6</v>
@@ -1477,20 +1482,20 @@
         <v>0.06</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -1500,12 +1505,12 @@
         <v>-6</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -1525,20 +1530,20 @@
         <v>0.02</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="I14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -1548,12 +1553,12 @@
         <v>-2</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
@@ -1573,20 +1578,20 @@
         <v>0.01</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -1596,12 +1601,12 @@
         <v>-1</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
@@ -1621,20 +1626,20 @@
         <v>0.04</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -1644,12 +1649,12 @@
         <v>-4</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
@@ -1669,20 +1674,20 @@
         <v>1.5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1692,12 +1697,12 @@
         <v>-1</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -1717,20 +1722,20 @@
         <v>0.35</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -1740,12 +1745,12 @@
         <v>-1</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -1765,20 +1770,20 @@
         <v>0.7</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -1788,12 +1793,12 @@
         <v>-1</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
@@ -1813,20 +1818,20 @@
         <v>0.9</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -1836,12 +1841,12 @@
         <v>-1</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
@@ -1861,20 +1866,20 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -1884,12 +1889,12 @@
         <v>-1</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B22" s="2">
         <v>3</v>
@@ -1909,20 +1914,20 @@
         <v>1.2000000000000002</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -1932,12 +1937,12 @@
         <v>-3</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -1957,20 +1962,20 @@
         <v>0.4</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -1980,12 +1985,12 @@
         <v>-2</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B24" s="2">
         <v>2</v>
@@ -2005,20 +2010,20 @@
         <v>0.3</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -2028,12 +2033,12 @@
         <v>-2</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2">
         <v>20</v>
@@ -2053,20 +2058,20 @@
         <v>2.4</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -2076,7 +2081,7 @@
         <v>-20</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
@@ -2349,6 +2354,10 @@
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I5" r:id="rId1" xr:uid="{D2D254FF-9EED-4110-85D6-A375ADBB5753}"/>
+    <hyperlink ref="J5" r:id="rId2" xr:uid="{9A7EAE44-DCBD-4788-8A8E-FAD89FC25B65}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>